--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129632153</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129632150</v>
       </c>
       <c r="B7" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98673</v>
+        <v>98685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129632153</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129632150</v>
       </c>
       <c r="B7" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98691</v>
+        <v>98695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129632153</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129632150</v>
       </c>
       <c r="B7" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129632153</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129632150</v>
       </c>
       <c r="B7" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,6 +1491,357 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129987451</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sätterstugan, Sätterstugan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>524018</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6537459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129987457</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sätterstugan, Sätterstugan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524018</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6537459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129990186</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sätterstugan, Sätterstugan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524041</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6537779</v>
+      </c>
+      <c r="S11" t="n">
+        <v>70</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>129632151</v>
       </c>
       <c r="B4" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129632152</v>
       </c>
       <c r="B5" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129632149</v>
       </c>
       <c r="B8" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -1611,27 +1611,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129987457</v>
+        <v>129990186</v>
       </c>
       <c r="B10" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524018</v>
+        <v>524041</v>
       </c>
       <c r="R10" t="n">
-        <v>6537459</v>
+        <v>6537779</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,27 +1728,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129990186</v>
+        <v>129987457</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524041</v>
+        <v>524018</v>
       </c>
       <c r="R11" t="n">
-        <v>6537779</v>
+        <v>6537459</v>
       </c>
       <c r="S11" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>129987451</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>129987457</v>
       </c>
       <c r="B11" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -1611,27 +1611,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129987457</v>
+        <v>129990186</v>
       </c>
       <c r="B10" t="n">
-        <v>58113</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524018</v>
+        <v>524041</v>
       </c>
       <c r="R10" t="n">
-        <v>6537459</v>
+        <v>6537779</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,27 +1728,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129990186</v>
+        <v>129987457</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>58113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524041</v>
+        <v>524018</v>
       </c>
       <c r="R11" t="n">
-        <v>6537779</v>
+        <v>6537459</v>
       </c>
       <c r="S11" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>129987451</v>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,27 +1611,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129990186</v>
+        <v>129987457</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>58198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524041</v>
+        <v>524018</v>
       </c>
       <c r="R10" t="n">
-        <v>6537779</v>
+        <v>6537459</v>
       </c>
       <c r="S10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,27 +1728,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129987457</v>
+        <v>129990186</v>
       </c>
       <c r="B11" t="n">
-        <v>58113</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524018</v>
+        <v>524041</v>
       </c>
       <c r="R11" t="n">
-        <v>6537459</v>
+        <v>6537779</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -1611,27 +1611,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129987457</v>
+        <v>129990186</v>
       </c>
       <c r="B10" t="n">
-        <v>58198</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524018</v>
+        <v>524041</v>
       </c>
       <c r="R10" t="n">
-        <v>6537459</v>
+        <v>6537779</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,27 +1728,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129990186</v>
+        <v>129987457</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>58198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524041</v>
+        <v>524018</v>
       </c>
       <c r="R11" t="n">
-        <v>6537779</v>
+        <v>6537459</v>
       </c>
       <c r="S11" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129632148</v>
+        <v>129632151</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sätterstugan, Nrk</t>
+          <t>Sätterbo, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523953</v>
+        <v>524014</v>
       </c>
       <c r="R2" t="n">
-        <v>6537654</v>
+        <v>6537455</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,54 +790,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129632147</v>
+        <v>129632152</v>
       </c>
       <c r="B3" t="n">
-        <v>4773</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sätterstugan, Nrk</t>
+          <t>Sätterbo, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523980</v>
+        <v>524043</v>
       </c>
       <c r="R3" t="n">
-        <v>6537672</v>
+        <v>6537444</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -909,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129632151</v>
+        <v>129632154</v>
       </c>
       <c r="B4" t="n">
-        <v>92926</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524014</v>
+        <v>524103</v>
       </c>
       <c r="R4" t="n">
-        <v>6537455</v>
+        <v>6537434</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1024,55 +1020,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129632152</v>
+        <v>129990186</v>
       </c>
       <c r="B5" t="n">
-        <v>92926</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sätterbo, Nrk</t>
+          <t>Sätterstugan, Sätterstugan, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524043</v>
+        <v>524041</v>
       </c>
       <c r="R5" t="n">
-        <v>6537444</v>
+        <v>6537779</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,75 +1114,76 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129632153</v>
+        <v>129990277</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sätterbo, Nrk</t>
+          <t>Sätterstugan, Sätterstugan, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524067</v>
+        <v>524130</v>
       </c>
       <c r="R6" t="n">
-        <v>6537443</v>
+        <v>6537701</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,22 +1207,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,16 +1238,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,7 +1282,7 @@
         <v>129632150</v>
       </c>
       <c r="B7" t="n">
-        <v>56930</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129632149</v>
+        <v>129632147</v>
       </c>
       <c r="B8" t="n">
-        <v>98715</v>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,42 +1414,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sätterbo, Nrk</t>
+          <t>Sätterstugan, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524016</v>
+        <v>523980</v>
       </c>
       <c r="R8" t="n">
-        <v>6537483</v>
+        <v>6537672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,53 +1520,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129987451</v>
+        <v>129632148</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sätterstugan, Sätterstugan, Nrk</t>
+          <t>Sätterstugan, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524018</v>
+        <v>523953</v>
       </c>
       <c r="R9" t="n">
-        <v>6537459</v>
+        <v>6537654</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,22 +1594,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,76 +1618,76 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129990186</v>
+        <v>129632191</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sätterstugan, Sätterstugan, Nrk</t>
+          <t>Sätterbo, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524041</v>
+        <v>524075</v>
       </c>
       <c r="R10" t="n">
-        <v>6537779</v>
+        <v>6537342</v>
       </c>
       <c r="S10" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,22 +1711,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,23 +1735,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1731,7 +1757,7 @@
         <v>129987457</v>
       </c>
       <c r="B11" t="n">
-        <v>58198</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1842,6 +1868,354 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129632153</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sätterbo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>524067</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6537443</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129987451</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sätterstugan, Sätterstugan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>524018</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6537459</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129632149</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sätterbo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>524016</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6537483</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52525-2025 artfynd.xlsx
+++ b/artfynd/A 52525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632152</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632154</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129990186</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1276,6 +1301,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129990277</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632150</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,6 +1552,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632147</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1634,6 +1674,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632148</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632191</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1868,6 +1918,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987457</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1983,6 +2038,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632153</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2100,6 +2160,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987451</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2216,8 +2281,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632149</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>